--- a/output/upload/S00027_2204_시그니처H보장보험_무배당.xlsx
+++ b/output/upload/S00027_2204_시그니처H보장보험_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2204A02</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2204A02</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2777,11 +2817,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2204A02</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2860,11 +2920,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2204A02</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2943,11 +3023,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2204A02</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3026,11 +3126,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2204A02</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3109,11 +3229,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2204A02</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3192,11 +3332,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2204A02</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3274,8 +3434,31 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2204A02</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3319,8 +3502,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2204A02</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3364,8 +3570,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2204A02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3409,8 +3638,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2204A02</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>22042</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처H보장보험 무배당 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_2204_시그니처H보장보험_무배당.xlsx
+++ b/output/upload/S00027_2204_시그니처H보장보험_무배당.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>2204002</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">

--- a/output/upload/S00027_2204_시그니처H보장보험_무배당.xlsx
+++ b/output/upload/S00027_2204_시그니처H보장보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
